--- a/window/windowList_protocolCore.xlsx
+++ b/window/windowList_protocolCore.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A52BC6-13C4-400C-8414-07501D807B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="3465" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove finestre" sheetId="1" r:id="rId1"/>

--- a/window/windowList_protocolCore.xlsx
+++ b/window/windowList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\window\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A52BC6-13C4-400C-8414-07501D807B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7709C45-4331-4704-9528-300655558470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove finestre" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
   <si>
     <t>Finestra</t>
   </si>
@@ -163,6 +163,15 @@
   </si>
   <si>
     <t>Scheda</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>AWI</t>
+  </si>
+  <si>
+    <t>Note per Patch</t>
   </si>
 </sst>
 </file>
@@ -194,7 +203,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -248,11 +257,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,9 +296,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -292,6 +313,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,128 +603,246 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="45.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
     <col min="7" max="7" width="18.140625" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="L1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="D2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="I2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="14">
         <v>5</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="L2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="14">
         <v>5</v>
       </c>
+      <c r="L3" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -713,19 +861,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>18</v>
       </c>
     </row>
@@ -805,82 +953,82 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -921,22 +1069,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
